--- a/fev_esocial.xlsx
+++ b/fev_esocial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jpvon\Downloads\sistema_evelly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D8BCBB-FE57-4F6F-B6BF-B3D63461360D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2531606F-DDCC-488A-AA70-05E181BF6778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{123855A9-24C8-4BD4-90ED-CCC29BCA547F}"/>
   </bookViews>
@@ -2894,8 +2894,8 @@
         <v>38</v>
       </c>
       <c r="G35" s="7"/>
-      <c r="H35" s="13" t="s">
-        <v>81</v>
+      <c r="H35" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="I35" s="9">
         <v>46080</v>
